--- a/uat-test-plans-reduced30/G2-16248-meganav-components-set-up.xlsx
+++ b/uat-test-plans-reduced30/G2-16248-meganav-components-set-up.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~27% — 8/11 checks retained, lowest-priority sections dropped] 17 UI-testable child stories/bugs/technical stories mapped to 11 business checks and 17 coverage rows. 10 backend, BO, evaluation, and QA task items excluded from business execution scope.</t>
+          <t>[Reduced V2 ~27% — 8/11 checks retained; AC and core-case coverage guardrails enforced] 17 UI-testable child stories/bugs/technical stories mapped to 11 business checks and 17 coverage rows. 10 backend, BO, evaluation, and QA task items excluded from business execution scope.</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=14476; payload_chars=14472; est_tokens~3618; checklist_rows=8; matrix_rows=12; exploratory_rows=3</t>
+          <t>payload_bytes=16538; payload_chars=16534; est_tokens~4134; checklist_rows=8; matrix_rows=17; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
     <row r="3" ht="79" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>UAT-002</t>
+          <t>UAT-004</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -825,141 +825,140 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Mobile Navigation</t>
+          <t>Product Carousel</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Mobile hamburger navigation exposes nested menu and closes/returns reliably</t>
+          <t>Product carousel and product-list style modules show valid data and interactions</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>On mobile web for NAP and MRP, open hamburger menu, drill into nested levels, and navigate back/close repeatedly.</t>
+          <t>Open navigation entries with product carousel/list content and verify item load, image rendering, and click-through behavior.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Menu opens and closes without visual breakage.
-Nested levels are reachable and reversible.
-Scroll and tap interactions remain stable during navigation.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="94" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>UAT-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Flyout Templates</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>All configured flyout template variants render correctly</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Validate no-flyout, text+image, and multi-column variants where configured in desktop and mobile contexts.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Configured template variant matches expected layout.
-No fallback-to-wrong-template behavior is observed.
-Content blocks render without overlap or clipping.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="79" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>UAT-004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Product Carousel</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Product carousel and product-list style modules show valid data and interactions</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Open navigation entries with product carousel/list content and verify item load, image rendering, and click-through behavior.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Product data is populated with valid items.
 Item click-through opens the correct product page.
 Carousel/list visuals align with active brand styling.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="79" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="79" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>UAT-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Sane, Sridevi Mayuresh || LuxExperience</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Trending Designers</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Trending designers module is visible and navigable where configured</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Verify the trending designers section appears in configured meganav nodes and links resolve as intended.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Module is rendered in configured positions.
 Designer links are clickable and route correctly.
 Module styling remains consistent across brands.</t>
         </is>
       </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="64" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>UAT-006</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>No-Flyout Behavior</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Navigation supports no-flyout categories without empty overlays</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Open categories configured as no-flyout and confirm no blank flyout panel appears.</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>No-flyout items route directly without showing empty panels.
+Header state remains stable after repeated navigation.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="94" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>UAT-007</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>UX Feedback Fixes</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>UX feedback fixes for spacing, typography, and card layout are reflected in navigation</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Review corrected areas from UX feedback tickets, including title spacing, card spacing, and header/navigation visual details.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Agreed spacing and typography adjustments are visible.
+Marketing cards and navigation titles match intended presentation.
+No major regressions appear in corrected areas.</t>
+        </is>
+      </c>
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr"/>
     </row>
-    <row r="7" ht="64" customHeight="1">
+    <row r="7" ht="79" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-009</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
@@ -969,95 +968,96 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>No-Flyout Behavior</t>
+          <t>Mobile Auth Entry</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Navigation supports no-flyout categories without empty overlays</t>
+          <t>Mobile login/register entry point is present and routes correctly for guests</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Open categories configured as no-flyout and confirm no blank flyout panel appears.</t>
+          <t>On mobile web, verify guest users can access login/register from navigation and return to browsing state after navigation.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>No-flyout items route directly without showing empty panels.
-Header state remains stable after repeated navigation.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="79" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>UAT-009</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Mobile Auth Entry</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Mobile login/register entry point is present and routes correctly for guests</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>On mobile web, verify guest users can access login/register from navigation and return to browsing state after navigation.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Login/Register entry is visible for guests.
 Tap action routes to authentication flow correctly.
 Returning from auth does not break menu state.</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9" ht="64" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="64" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>UAT-010</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Sane, Sridevi Mayuresh || LuxExperience</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Mobile Service Links</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Customer service links are available and correctly mapped in mobile navigation</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Open account/service area from mobile menu and validate customer service link presence, labels, and destinations.</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>All expected service links are present.
 Each link routes to the intended destination.
 Spacing and hover/active states are acceptable.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="79" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>UAT-011</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Sane, Sridevi Mayuresh || LuxExperience</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Regression Sanity</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Meganav changes do not regress core browse journey from homepage to PLP/PDP</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Execute a short browse journey for both brands from homepage through category to product page using meganav entry points.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Journey completes without broken navigation transitions.
+No severe UI regressions block browsing.
+Core pages remain reachable from updated meganav.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1087,7 @@
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="50" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="25" customHeight="1">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>UAT-002</t>
+          <t>UAT-011</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-001, UAT-011</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-003</t>
+          <t>UAT-011</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-001, UAT-011</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-002</t>
+          <t>UAT-001</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1465,25 +1465,25 @@
       </c>
       <c r="K7" s="5" t="inlineStr"/>
     </row>
-    <row r="8" ht="19" customHeight="1">
+    <row r="8" ht="34" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>COV-008</t>
+          <t>COV-007</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>G2-19002</t>
+          <t>G2-18710</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>AC-Trending-Designers</t>
+          <t>AC-RedText-Highlight</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Trending designers carousel in meganav</t>
+          <t>Red text support in meganav and nested categories</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -1493,60 +1493,64 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>UAT-005</t>
+          <t>UAT-007</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Full</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>PR #456 from GitHub MCP.</t>
+          <t>No key-based GitHub hit and no Jira fallback PR/commit URL.</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Available</t>
+          <t>Unavailable</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="inlineStr"/>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Implementation evidence gap despite clear business expectation.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>COV-009</t>
+          <t>COV-008</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>G2-19618</t>
+          <t>G2-19002</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>AC-NoFlyout</t>
+          <t>AC-Trending-Designers</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>No-flyout navigation behavior</t>
+          <t>Trending designers carousel in meganav</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>UAT-006</t>
+          <t>UAT-005</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1556,7 +1560,7 @@
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>PR #299 from GitHub MCP.</t>
+          <t>PR #456 from GitHub MCP.</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
@@ -1574,32 +1578,32 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>COV-011</t>
+          <t>COV-009</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>G2-20433</t>
+          <t>G2-19618</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Bugfix-Carousel-UX</t>
+          <t>AC-NoFlyout</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Product carousel/list UX corrections</t>
+          <t>No-flyout navigation behavior</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-006</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1609,7 +1613,7 @@
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>PR #395 from GitHub MCP.</t>
+          <t>PR #299 from GitHub MCP.</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -1619,7 +1623,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K10" s="5" t="inlineStr"/>
@@ -1627,22 +1631,22 @@
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>COV-015</t>
+          <t>COV-010</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>G2-20612</t>
+          <t>G2-20396</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>AC-Carousel-Data-Integration</t>
+          <t>AC-UX-Feedback-Bundle</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Product carousel integration with real product data</t>
+          <t>Consolidated UX review fixes on meganav/header</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -1652,80 +1656,84 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-007, UAT-011</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
+          <t>Partial</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>PR #501 from GitHub MCP; AC phrasing spans multiple visual defects.</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Broad ticket scope may hide per-defect acceptance granularity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>COV-011</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>G2-20433</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Bugfix-Carousel-UX</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Product carousel/list UX corrections</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>UAT-004, UAT-007</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>PR #420 from GitHub MCP.</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>PR #395 from GitHub MCP.</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>COV-016</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>G2-21400</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>AC-Mobile-Auth-Entry</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Login/Register entry in mobile navigation for guests</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>UAT-009</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>Full</t>
-        </is>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>PR #516 from GitHub MCP.</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Available</t>
-        </is>
-      </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K12" s="5" t="inlineStr"/>
@@ -1733,55 +1741,320 @@
     <row r="13" ht="34" customHeight="1">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>COV-012</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>G2-20443</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Bugfix-MRP-Title-Styling</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>MRP nav column title styling exceptions</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>UAT-007</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>PR #438 from GitHub MCP; Jira comment references discussion #424.</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr"/>
+    </row>
+    <row r="14" ht="34" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>COV-013</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>G2-20572</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Bugfix-Marketing-Cards</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Marketing card spacing/layout corrections in meganav</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>UAT-007</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>PR #367 from GitHub MCP.</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr"/>
+    </row>
+    <row r="15" ht="19" customHeight="1">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>COV-014</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>G2-20573</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Bugfix-Header-Nav-UX</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>Header and nav UX adjustment bundle</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>UAT-007, UAT-011</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>PR #373 from GitHub MCP.</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16" ht="34" customHeight="1">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>COV-015</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>G2-20612</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>AC-Carousel-Data-Integration</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Product carousel integration with real product data</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>UAT-004</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>PR #420 from GitHub MCP.</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr"/>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>COV-016</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>G2-21400</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>AC-Mobile-Auth-Entry</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Login/Register entry in mobile navigation for guests</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>UAT-009</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>PR #516 from GitHub MCP.</t>
+        </is>
+      </c>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Available</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr"/>
+    </row>
+    <row r="18" ht="34" customHeight="1">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
           <t>COV-017</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>G2-22019</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>AC-Mobile-Service-Links</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Customer service link group in mobile navigation</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>UAT-010</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>Full</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
         <is>
           <t>PR #552 from GitHub MCP.</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>Available</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/uat-test-plans-reduced30/G2-16248-meganav-components-set-up.xlsx
+++ b/uat-test-plans-reduced30/G2-16248-meganav-components-set-up.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~27% — 8/11 checks retained; AC and core-case coverage guardrails enforced] 17 UI-testable child stories/bugs/technical stories mapped to 11 business checks and 17 coverage rows. 10 backend, BO, evaluation, and QA task items excluded from business execution scope.</t>
+          <t>[Reduced V2 ~27% — 8/11 checks retained; AC coverage guardrail enforced] 17 UI-testable child stories/bugs/technical stories mapped to 11 business checks and 17 coverage rows. 10 backend, BO, evaluation, and QA task items excluded from business execution scope.</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=16538; payload_chars=16534; est_tokens~4134; checklist_rows=8; matrix_rows=17; exploratory_rows=3</t>
+          <t>payload_bytes=16505; payload_chars=16501; est_tokens~4126; checklist_rows=8; matrix_rows=17; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -776,10 +776,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="94" customHeight="1">
+    <row r="2" ht="79" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-002</t>
         </is>
       </c>
       <c r="B2" s="5" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Desktop Main Navigation</t>
+          <t>Mobile Navigation</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Desktop top navigation opens and routes correctly for major categories</t>
+          <t>Mobile hamburger navigation exposes nested menu and closes/returns reliably</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>On NAP and MRP desktop, hover/click top-level categories and verify the expected first-level routing and flyout behavior.</t>
+          <t>On mobile web for NAP and MRP, open hamburger menu, drill into nested levels, and navigate back/close repeatedly.</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Top-level categories open consistently on desktop.
-Category links route to the expected listing pages.
-No blocked or dead-end navigation state appears.</t>
+          <t>Menu opens and closes without visual breakage.
+Nested levels are reachable and reversible.
+Scroll and tap interactions remain stable during navigation.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr"/>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>UAT-011</t>
+          <t>UAT-002, UAT-011</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-011</t>
+          <t>UAT-011</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>UAT-001, UAT-011</t>
+          <t>UAT-011</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-002</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
